--- a/data/trans_orig/P57B5_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57B5_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido rebosante de energía en 2023</t>
+          <t>Población según se ha sentido rebosante de energía en 2023 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>110547</t>
+          <t>109217</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>147889</t>
+          <t>147884</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>116648</t>
+          <t>116208</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>150507</t>
+          <t>152118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>236404</t>
+          <t>235651</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>286837</t>
+          <t>286516</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>178930</t>
+          <t>179744</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>219606</t>
+          <t>220148</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>241004</t>
+          <t>244319</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281722</t>
+          <t>283998</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>432519</t>
+          <t>434264</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>491744</t>
+          <t>491857</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,04%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117073</t>
+          <t>117245</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152626</t>
+          <t>154107</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>208329</t>
+          <t>209639</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>246805</t>
+          <t>245704</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>334193</t>
+          <t>335956</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>386363</t>
+          <t>389183</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37924</t>
+          <t>38347</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61585</t>
+          <t>61263</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110126</t>
+          <t>111813</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145137</t>
+          <t>146444</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>155822</t>
+          <t>156805</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>198768</t>
+          <t>199101</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>991293</t>
+          <t>992604</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1504694</t>
+          <t>1467912</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>477212</t>
+          <t>488527</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>755249</t>
+          <t>755714</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1556645</t>
+          <t>1574018</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2240946</t>
+          <t>2293895</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>50,72%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>558710</t>
+          <t>559071</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>905099</t>
+          <t>906718</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>995499</t>
+          <t>992936</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1431251</t>
+          <t>1422605</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1636292</t>
+          <t>1632059</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2302597</t>
+          <t>2258134</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>197170</t>
+          <t>209431</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>340690</t>
+          <t>342878</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>256981</t>
+          <t>267012</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>414901</t>
+          <t>415813</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>524250</t>
+          <t>507936</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>732697</t>
+          <t>726277</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38814</t>
+          <t>37669</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75305</t>
+          <t>74209</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52252</t>
+          <t>51723</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86460</t>
+          <t>90338</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>99708</t>
+          <t>98475</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152590</t>
+          <t>150380</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>241450</t>
+          <t>242519</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299596</t>
+          <t>298079</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>215509</t>
+          <t>217173</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>259824</t>
+          <t>259973</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>468070</t>
+          <t>468352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>540902</t>
+          <t>541961</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>243295</t>
+          <t>241767</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>296444</t>
+          <t>297128</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>271083</t>
+          <t>273519</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>317902</t>
+          <t>316182</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>526709</t>
+          <t>526052</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>595901</t>
+          <t>596167</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68269</t>
+          <t>68129</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102498</t>
+          <t>102472</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84865</t>
+          <t>86236</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119125</t>
+          <t>119556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>163416</t>
+          <t>163352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>210149</t>
+          <t>208281</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17190</t>
+          <t>15959</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39249</t>
+          <t>39531</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20076</t>
+          <t>19924</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38139</t>
+          <t>38243</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40123</t>
+          <t>41419</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68833</t>
+          <t>71297</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1378401</t>
+          <t>1380225</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1991343</t>
+          <t>2041719</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>849800</t>
+          <t>839265</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1124633</t>
+          <t>1125386</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2343961</t>
+          <t>2353611</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3076153</t>
+          <t>3096144</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>961146</t>
+          <t>953951</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1375067</t>
+          <t>1382045</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1538806</t>
+          <t>1540320</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2046009</t>
+          <t>2057028</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2701918</t>
+          <t>2652107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3352164</t>
+          <t>3314570</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>383926</t>
+          <t>388679</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>565333</t>
+          <t>561809</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>568903</t>
+          <t>563653</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>753836</t>
+          <t>754043</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1035213</t>
+          <t>1041914</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1291214</t>
+          <t>1296959</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101465</t>
+          <t>97336</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>157128</t>
+          <t>155442</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>181716</t>
+          <t>187132</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>255410</t>
+          <t>254778</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>308777</t>
+          <t>310423</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>400636</t>
+          <t>402395</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B5_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57B5_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>128285</t>
+          <t>148856</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109217</t>
+          <t>129190</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>147884</t>
+          <t>172624</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>132365</t>
+          <t>147314</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>116208</t>
+          <t>128988</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152118</t>
+          <t>164986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>260650</t>
+          <t>296170</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>235651</t>
+          <t>268377</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>286516</t>
+          <t>324105</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>199276</t>
+          <t>226440</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>179744</t>
+          <t>203571</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>220148</t>
+          <t>249491</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>263797</t>
+          <t>293806</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>244319</t>
+          <t>274537</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283998</t>
+          <t>314951</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>463073</t>
+          <t>520246</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>434264</t>
+          <t>492923</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>491857</t>
+          <t>553406</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>134231</t>
+          <t>145044</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117245</t>
+          <t>128299</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>154107</t>
+          <t>164895</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>226858</t>
+          <t>244710</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>209639</t>
+          <t>225566</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>245704</t>
+          <t>263797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>361089</t>
+          <t>389754</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>335956</t>
+          <t>359769</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>389183</t>
+          <t>415872</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48809</t>
+          <t>53505</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38347</t>
+          <t>41699</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61263</t>
+          <t>68013</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>126398</t>
+          <t>129811</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>111813</t>
+          <t>115027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>146444</t>
+          <t>146900</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>175208</t>
+          <t>183316</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>156805</t>
+          <t>162732</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>199101</t>
+          <t>204671</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>510602</t>
+          <t>573845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>510602</t>
+          <t>573845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>510602</t>
+          <t>573845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>749418</t>
+          <t>815641</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>749418</t>
+          <t>815641</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>749418</t>
+          <t>815641</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1260020</t>
+          <t>1389486</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1260020</t>
+          <t>1389486</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1260020</t>
+          <t>1389486</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1149707</t>
+          <t>987812</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>992604</t>
+          <t>929880</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1467912</t>
+          <t>1036854</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>665193</t>
+          <t>750364</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>488527</t>
+          <t>711261</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>755714</t>
+          <t>795984</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1814900</t>
+          <t>1738176</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1574018</t>
+          <t>1671308</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2293895</t>
+          <t>1807308</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>41,11%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>790978</t>
+          <t>867546</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>559071</t>
+          <t>811598</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>906718</t>
+          <t>917055</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1138853</t>
+          <t>939545</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>992936</t>
+          <t>891491</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1422605</t>
+          <t>979575</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1929832</t>
+          <t>1807092</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1632059</t>
+          <t>1739781</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2258134</t>
+          <t>1874129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>42,63%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>290575</t>
+          <t>312363</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>209431</t>
+          <t>280495</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>342878</t>
+          <t>348169</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>360035</t>
+          <t>397717</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>267012</t>
+          <t>364905</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>415813</t>
+          <t>429339</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>650610</t>
+          <t>710080</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>507936</t>
+          <t>661564</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>726277</t>
+          <t>760349</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56647</t>
+          <t>60327</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37669</t>
+          <t>46645</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74209</t>
+          <t>76545</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>70541</t>
+          <t>80405</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51723</t>
+          <t>66181</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90338</t>
+          <t>97332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>127188</t>
+          <t>140732</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>98475</t>
+          <t>120926</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>150380</t>
+          <t>165511</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2287907</t>
+          <t>2228049</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2287907</t>
+          <t>2228049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2287907</t>
+          <t>2228049</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2234623</t>
+          <t>2168031</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2234623</t>
+          <t>2168031</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2234623</t>
+          <t>2168031</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4522530</t>
+          <t>4396080</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4522530</t>
+          <t>4396080</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4522530</t>
+          <t>4396080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>268403</t>
+          <t>298575</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>242519</t>
+          <t>272118</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>298079</t>
+          <t>331003</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>236409</t>
+          <t>260515</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>217173</t>
+          <t>236149</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>259973</t>
+          <t>284227</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>504812</t>
+          <t>559090</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>468352</t>
+          <t>518516</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>541961</t>
+          <t>594407</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,09%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>268232</t>
+          <t>292119</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>241767</t>
+          <t>264160</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>297128</t>
+          <t>319848</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>294262</t>
+          <t>323399</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>273519</t>
+          <t>300325</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>316182</t>
+          <t>347569</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>562494</t>
+          <t>615518</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>526052</t>
+          <t>580757</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>596167</t>
+          <t>654804</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,27%</t>
         </is>
       </c>
     </row>
@@ -2089,17 +2089,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>83971</t>
+          <t>92466</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68129</t>
+          <t>75324</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102472</t>
+          <t>111404</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>101852</t>
+          <t>120789</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86236</t>
+          <t>103346</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119556</t>
+          <t>139345</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>185823</t>
+          <t>213255</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>163352</t>
+          <t>188675</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>208281</t>
+          <t>239347</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26016</t>
+          <t>28427</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15959</t>
+          <t>17860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39531</t>
+          <t>44776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27941</t>
+          <t>30174</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>21914</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38243</t>
+          <t>40557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>53957</t>
+          <t>58601</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41419</t>
+          <t>44997</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71297</t>
+          <t>75735</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1546395</t>
+          <t>1435243</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1380225</t>
+          <t>1369393</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2041719</t>
+          <t>1505037</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1033967</t>
+          <t>1158192</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>839265</t>
+          <t>1107614</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1125386</t>
+          <t>1208720</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2580362</t>
+          <t>2593436</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2353611</t>
+          <t>2510766</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3096144</t>
+          <t>2676833</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1258487</t>
+          <t>1386105</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>953951</t>
+          <t>1328142</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1382045</t>
+          <t>1452591</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1696912</t>
+          <t>1556750</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1540320</t>
+          <t>1500204</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2057028</t>
+          <t>1610565</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2955399</t>
+          <t>2942855</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2652107</t>
+          <t>2855165</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3314570</t>
+          <t>3019048</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>41,75%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>508777</t>
+          <t>549873</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>388679</t>
+          <t>509410</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>561809</t>
+          <t>591189</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>688745</t>
+          <t>763216</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>563653</t>
+          <t>722753</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>754043</t>
+          <t>806313</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1197522</t>
+          <t>1313090</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1041914</t>
+          <t>1265170</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1296959</t>
+          <t>1381118</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>131473</t>
+          <t>142259</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97336</t>
+          <t>118977</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>155442</t>
+          <t>166894</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>224880</t>
+          <t>240391</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>187132</t>
+          <t>216307</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>254778</t>
+          <t>265663</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>356353</t>
+          <t>382649</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>310423</t>
+          <t>350365</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>402395</t>
+          <t>418956</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3445132</t>
+          <t>3513481</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3445132</t>
+          <t>3513481</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3445132</t>
+          <t>3513481</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3644504</t>
+          <t>3718549</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3644504</t>
+          <t>3718549</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3644504</t>
+          <t>3718549</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7089637</t>
+          <t>7232030</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7089637</t>
+          <t>7232030</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7089637</t>
+          <t>7232030</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
